--- a/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
+++ b/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTLDI ATLAS 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RTLDI ATLAS 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,14 +515,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source equation: ΔG = η × (1 − R) × G₀   |   η = 0.3 (Hubbard, Causality and Attraction v3, DOI 10.5281/zenodo.19468550)   |   R = R from 8 V-Dem components (crosswalk, year=2024) + real WB socio #9 + 2026-fresh G0 (GDP is the more dynamic variable). See docs/indicator_crosswalk.md</t>
+          <t>Source equation: ΔG = η × (1 − R) × G₀   |   η = 0.36 (Hubbard, Causality and Attraction v3, DOI 10.5281/zenodo.19468550)   |   R = R from 8 V-Dem components (crosswalk, year=2024) + real WB socio #9 + 2026-fresh G0 (GDP is the more dynamic variable). See docs/indicator_crosswalk.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Countries: 193 | With GDP: 187 | Est. global capital exclusions: $17,490,547,087,096 | Avg R: 0.326</t>
+          <t>Countries: 193 | With GDP: 187 | Est. global capital exclusions: $19,285,629,457,515 | Avg R: 0.326</t>
         </is>
       </c>
     </row>
@@ -694,10 +694,10 @@
         <v>2024</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>11271.20543788731</v>
+        <v>13525.44652546477</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3833460817430.825</v>
+        <v>4600152980916.988</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>2</v>
@@ -812,10 +812,10 @@
         <v>2024</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>4331.61037396756</v>
+        <v>5197.932448761071</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>537013003140.077</v>
+        <v>644415603768.0923</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>4</v>
@@ -841,28 +841,28 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>143533851</v>
+        <v>69226000</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>14889.0185546875</v>
+        <v>53246.3676145108</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>2026</v>
@@ -871,16 +871,16 @@
         <v>2024</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3722.254638671875</v>
+        <v>8519.418818321727</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>534269542691.1877</v>
+        <v>589765287117.1399</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>5</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -900,28 +900,28 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>69226000</v>
+        <v>143533851</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.556</v>
+        <v>0.111</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>53246.3676145108</v>
+        <v>14889.0185546875</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>2026</v>
@@ -930,16 +930,16 @@
         <v>2024</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7099.515681934773</v>
+        <v>3722.254638671875</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>491471072597.6166</v>
+        <v>534269542691.1877</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>6</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         <v>2024</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>3310.015619132344</v>
+        <v>3546.445306213225</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>433151977105.387</v>
+        <v>464091404041.486</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>7</v>
@@ -1048,10 +1048,10 @@
         <v>2024</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>7247.727981663001</v>
+        <v>8697.273577995602</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>375077641881.3608</v>
+        <v>450093170257.633</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>8</v>
@@ -1107,10 +1107,10 @@
         <v>2024</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1718.424812969433</v>
+        <v>2062.10977556332</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>364303608157.3118</v>
+        <v>437164329788.7741</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>9</v>
@@ -1166,10 +1166,10 @@
         <v>2024</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>5384.712186102253</v>
+        <v>6461.654623322704</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>317443343632.4791</v>
+        <v>380932012358.9749</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
         <v>2024</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>3708.30033670229</v>
+        <v>3973.178932181025</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>317128879380.629</v>
+        <v>339780942193.5311</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>11</v>
@@ -1254,28 +1254,28 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>35300280</v>
+        <v>283487931</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>35121.6628687742</v>
+        <v>4925.43048751861</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>2026</v>
@@ -1284,16 +1284,16 @@
         <v>2024</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>8780.415717193549</v>
+        <v>1182.103317004466</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>309951133333.3331</v>
+        <v>335112023565.8333</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>12</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1313,28 +1313,28 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>283487931</v>
+        <v>35300280</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>4925.43048751861</v>
+        <v>35121.6628687742</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2026</v>
@@ -1343,16 +1343,16 @@
         <v>2024</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>985.086097503722</v>
+        <v>8780.415717193549</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>279260019638.1944</v>
+        <v>309951133333.3331</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>13</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         <v>2024</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>5434.034772247331</v>
+        <v>6520.841726696796</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>224363682663.3764</v>
+        <v>269236419196.0516</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>14</v>
@@ -1461,10 +1461,10 @@
         <v>2024</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>3073.538939039228</v>
+        <v>3688.246726847071</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>210696174831.0053</v>
+        <v>252835409797.2062</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>15</v>
@@ -1520,16 +1520,16 @@
         <v>2024</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>3532.676830692779</v>
+        <v>4239.212196831336</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>172567165274.2187</v>
+        <v>207080598329.0624</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>16</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         <v>2024</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1870.124410608514</v>
+        <v>2244.149292730217</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>156186419260.1562</v>
+        <v>187423703112.1874</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>17</v>
@@ -1608,28 +1608,28 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>10986400</v>
+        <v>36559233</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>50273.5060469837</v>
+        <v>25103.565661423</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>2026</v>
@@ -1638,16 +1638,16 @@
         <v>2024</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>12568.37651174592</v>
+        <v>4016.570505827679</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>138081211708.6454</v>
+        <v>146842736983.482</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>18</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1667,28 +1667,28 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>71668011</v>
+        <v>27196812</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.111</v>
+        <v>0.778</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>7346.62022142185</v>
+        <v>64603.9856308464</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>2026</v>
@@ -1697,16 +1697,16 @@
         <v>2024</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1836.655055355463</v>
+        <v>5168.318850467711</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>131629414710.4209</v>
+        <v>140561796132.2264</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>19</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -1726,28 +1726,28 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>36559233</v>
+        <v>10986400</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.556</v>
+        <v>0.111</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>25103.565661423</v>
+        <v>50273.5060469837</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>2026</v>
@@ -1756,16 +1756,16 @@
         <v>2024</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>3347.142088189733</v>
+        <v>12568.37651174592</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>122368947486.235</v>
+        <v>138081211708.6454</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>20</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -1785,16 +1785,16 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>100987686</v>
+        <v>71668011</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1806,7 +1806,7 @@
         <v>0.111</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>4717.29028732449</v>
+        <v>7346.62022142185</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>2026</v>
@@ -1815,10 +1815,10 @@
         <v>2024</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1179.322571831123</v>
+        <v>1836.655055355463</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>119097057576.7939</v>
+        <v>131629414710.4209</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>21</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
@@ -1844,28 +1844,28 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>91567738</v>
+        <v>9974400</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>5190.16959024821</v>
+        <v>54176.6844383302</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>2026</v>
@@ -1874,16 +1874,16 @@
         <v>2024</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1297.542397562052</v>
+        <v>13002.40426519925</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>118813022303.8539</v>
+        <v>129691181102.8034</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>22</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -1903,28 +1903,28 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>27196812</v>
+        <v>45696159</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.778</v>
+        <v>0.444</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>64603.9856308464</v>
+        <v>13969.7836603737</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>2026</v>
@@ -1933,16 +1933,16 @@
         <v>2024</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>4306.932375389762</v>
+        <v>2793.95673207474</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>117134830110.1888</v>
+        <v>127673091068.0077</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>23</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -1962,28 +1962,28 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>173562364</v>
+        <v>100987686</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2593.41611680774</v>
+        <v>4717.29028732449</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>2026</v>
@@ -1992,16 +1992,16 @@
         <v>2024</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>648.354029201935</v>
+        <v>1179.322571831123</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>112529858017.2129</v>
+        <v>119097057576.7939</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>24</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2021,28 +2021,28 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>9974400</v>
+        <v>91567738</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>54176.6844383302</v>
+        <v>5190.16959024821</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>2026</v>
@@ -2051,16 +2051,16 @@
         <v>2024</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10835.33688766604</v>
+        <v>1297.542397562052</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>108075984252.3362</v>
+        <v>118813022303.8539</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>25</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2080,28 +2080,28 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45696159</v>
+        <v>173562364</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>13969.7836603737</v>
+        <v>2593.41611680774</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>2026</v>
@@ -2110,16 +2110,16 @@
         <v>2024</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>2328.29727672895</v>
+        <v>648.354029201935</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>106394242556.6731</v>
+        <v>112529858017.2129</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>26</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2139,28 +2139,28 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>116538258</v>
+        <v>115843670</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>3338.47371395895</v>
+        <v>3984.8315387656</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>2026</v>
@@ -2169,16 +2169,16 @@
         <v>2024</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>834.6184284897375</v>
+        <v>956.359569303744</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>97264977750.89159</v>
+        <v>110788202347.765</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>27</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2198,28 +2198,28 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>251269164</v>
+        <v>116538258</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>1478.77277977996</v>
+        <v>3338.47371395895</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>2026</v>
@@ -2228,16 +2228,16 @@
         <v>2024</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>369.69319494499</v>
+        <v>834.6184284897375</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>92892500030.31667</v>
+        <v>97264977750.89159</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>28</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2257,28 +2257,28 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>115843670</v>
+        <v>17993485</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.333</v>
+        <v>0.778</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>3984.8315387656</v>
+        <v>67520.4218956281</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>2026</v>
@@ -2287,16 +2287,16 @@
         <v>2024</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>796.96630775312</v>
+        <v>5401.633751650247</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>92323501956.47087</v>
+        <v>97194215885.81245</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>29</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2316,28 +2316,28 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>17993485</v>
+        <v>251269164</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>67520.4218956281</v>
+        <v>1478.77277977996</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>2026</v>
@@ -2346,16 +2346,16 @@
         <v>2024</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>4501.361459708542</v>
+        <v>369.69319494499</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>80995179904.84375</v>
+        <v>92892500030.31667</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>30</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2375,28 +2375,28 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>20592571</v>
+        <v>35557673</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.111</v>
+        <v>0.444</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14154.6324958076</v>
+        <v>11874.4273684245</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>2026</v>
@@ -2405,16 +2405,16 @@
         <v>2024</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>3538.6581239519</v>
+        <v>2374.8854736849</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>72870068662.2063</v>
+        <v>84445401085.73779</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>31</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2434,28 +2434,28 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>35557673</v>
+        <v>52886363</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
         <v>0.444</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>11874.4273684245</v>
+        <v>7919.20886825345</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>2026</v>
@@ -2464,10 +2464,10 @@
         <v>2024</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>1979.07122807075</v>
+        <v>1583.84177365069</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>70371167571.44815</v>
+        <v>83763630975.85423</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>32</v>
@@ -2493,28 +2493,28 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46042015</v>
+        <v>64007187</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>IRQ</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>6073.61032342708</v>
+        <v>6267.186814093</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>2026</v>
@@ -2523,16 +2523,16 @@
         <v>2024</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1518.40258085677</v>
+        <v>1253.4373628186</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>69910314403.84612</v>
+        <v>80228999674.71698</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>33</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2552,28 +2552,28 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>52886363</v>
+        <v>20592571</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>7919.20886825345</v>
+        <v>14154.6324958076</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2026</v>
@@ -2582,16 +2582,16 @@
         <v>2024</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1319.868144708908</v>
+        <v>3538.6581239519</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>69803025813.21185</v>
+        <v>72870068662.2063</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>34</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2611,28 +2611,28 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46814308</v>
+        <v>46042015</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>IRQ</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>5752.99076651465</v>
+        <v>6073.61032342708</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2026</v>
@@ -2641,16 +2641,16 @@
         <v>2024</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1438.247691628663</v>
+        <v>1518.40258085677</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>67330570416.19323</v>
+        <v>69910314403.84612</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>35</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2670,28 +2670,28 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>64007187</v>
+        <v>34217848</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>6267.186814093</v>
+        <v>8452.37167056621</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>2026</v>
@@ -2700,16 +2700,16 @@
         <v>2024</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1044.531135682167</v>
+        <v>2028.569200935891</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>66857499728.93082</v>
+        <v>69413272575.10576</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>36</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2729,28 +2729,28 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>232679478</v>
+        <v>46814308</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.222</v>
+        <v>0.111</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>1084.16041805436</v>
+        <v>5752.99076651465</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>2026</v>
@@ -2759,16 +2759,16 @@
         <v>2024</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>252.970764212684</v>
+        <v>1438.247691628663</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>58861105366.26839</v>
+        <v>67330570416.19323</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>37</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2788,28 +2788,28 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>34217848</v>
+        <v>6036860</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>8452.37167056621</v>
+        <v>90674.066632628</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>2026</v>
@@ -2818,16 +2818,16 @@
         <v>2024</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1690.474334113242</v>
+        <v>10880.88799591536</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>57844393812.58813</v>
+        <v>65686397507.02161</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>38</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -2847,28 +2847,28 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>6036860</v>
+        <v>9177982</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
         <v>0.667</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>90674.066632628</v>
+        <v>58268.8787651601</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>2026</v>
@@ -2877,10 +2877,10 @@
         <v>2024</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>9067.4066632628</v>
+        <v>6992.265451819213</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>54738664589.18467</v>
+        <v>64174886456.01861</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>39</v>
@@ -2906,28 +2906,28 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>9177982</v>
+        <v>232679478</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.667</v>
+        <v>0.222</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>58268.8787651601</v>
+        <v>1084.16041805436</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>2026</v>
@@ -2936,16 +2936,16 @@
         <v>2024</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>5826.887876516009</v>
+        <v>271.04010451359</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>53479072046.68215</v>
+        <v>63065470035.28757</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>40</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -2965,28 +2965,28 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>2857822</v>
+        <v>19051804</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.222</v>
+        <v>0.556</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>76688.6941743178</v>
+        <v>20080.2096215595</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>2026</v>
@@ -2995,16 +2995,16 @@
         <v>2024</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>17894.02864067415</v>
+        <v>3212.83353944952</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>51137948717.94869</v>
+        <v>61210274878.21852</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>41</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3024,28 +3024,28 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>19051804</v>
+        <v>2857822</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.556</v>
+        <v>0.222</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>20080.2096215595</v>
+        <v>76688.6941743178</v>
       </c>
       <c r="G48" s="8" t="n">
         <v>2026</v>
@@ -3054,16 +3054,16 @@
         <v>2024</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>2677.3612828746</v>
+        <v>19172.17354357945</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>51008562398.51543</v>
+        <v>54790659340.65931</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>42</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
         <v>2024</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1257.543733723958</v>
+        <v>1347.368286132812</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>47610883675.95422</v>
+        <v>51011661081.37952</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>43</v>
@@ -3142,28 +3142,28 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>132059767</v>
+        <v>10405134</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1133.88279681719</v>
+        <v>24626.1481858973</v>
       </c>
       <c r="G50" s="8" t="n">
         <v>2026</v>
@@ -3172,16 +3172,16 @@
         <v>2024</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>283.4706992042975</v>
+        <v>3940.183709743567</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>37435074488.24661</v>
+        <v>40998139484.49892</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>44</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3201,28 +3201,28 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>10405134</v>
+        <v>4897263</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>24626.1481858973</v>
+        <v>32717.7186631255</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>2026</v>
@@ -3231,16 +3231,16 @@
         <v>2024</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>3283.486424786307</v>
+        <v>7852.25247915012</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>34165116237.08244</v>
+        <v>38454545532.80016</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>45</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3260,28 +3260,28 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>4897263</v>
+        <v>9005582</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.333</v>
+        <v>0.889</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>32717.7186631255</v>
+        <v>103998.186685604</v>
       </c>
       <c r="G52" s="8" t="n">
         <v>2026</v>
@@ -3290,16 +3290,16 @@
         <v>2024</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>6543.5437326251</v>
+        <v>4159.927467424161</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>32045454610.6668</v>
+        <v>37462567921.94061</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>46</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3319,28 +3319,28 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>9005582</v>
+        <v>132059767</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.889</v>
+        <v>0.111</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>103998.186685604</v>
+        <v>1133.88279681719</v>
       </c>
       <c r="G53" s="8" t="n">
         <v>2026</v>
@@ -3349,16 +3349,16 @@
         <v>2024</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>3466.606222853468</v>
+        <v>283.4706992042975</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>31218806601.61718</v>
+        <v>37435074488.24661</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>47</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3378,28 +3378,28 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>28405543</v>
+        <v>9562065</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>4217.59102643391</v>
+        <v>23292.3263882478</v>
       </c>
       <c r="G54" s="8" t="n">
         <v>2026</v>
@@ -3408,16 +3408,16 @@
         <v>2024</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>1054.397756608477</v>
+        <v>3726.772222119647</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>29950740814.44564</v>
+        <v>35635638228.10251</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>48</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3437,28 +3437,28 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>9562065</v>
+        <v>38081173</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.556</v>
+        <v>0.444</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>23292.3263882478</v>
+        <v>4153.1943359375</v>
       </c>
       <c r="G55" s="8" t="n">
         <v>2026</v>
@@ -3467,16 +3467,16 @@
         <v>2024</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>3105.64351843304</v>
+        <v>830.6388671875001</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>29696365190.08543</v>
+        <v>31631702401.89121</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>49</v>
       </c>
       <c r="L55" s="10" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3496,28 +3496,28 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>36361859</v>
+        <v>28405543</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>3161.70010632875</v>
+        <v>4217.59102643391</v>
       </c>
       <c r="G56" s="8" t="n">
         <v>2026</v>
@@ -3526,16 +3526,16 @@
         <v>2024</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>737.7300248100416</v>
+        <v>1054.397756608477</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>26825235142.20924</v>
+        <v>29950740814.44564</v>
       </c>
       <c r="K56" s="10" t="n">
         <v>50</v>
       </c>
       <c r="L56" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3555,28 +3555,28 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>18406359</v>
+        <v>18135478</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>6150.02571438505</v>
+        <v>6874.705739766</v>
       </c>
       <c r="G57" s="8" t="n">
         <v>2026</v>
@@ -3585,16 +3585,16 @@
         <v>2024</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>1435.006000023179</v>
+        <v>1649.92937754384</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>26413235603.58063</v>
+        <v>29922257928.00001</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>51</v>
       </c>
       <c r="L57" s="10" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3614,28 +3614,28 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>38081173</v>
+        <v>56432944</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>4153.1943359375</v>
+        <v>2132.43452097647</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>2026</v>
@@ -3644,16 +3644,16 @@
         <v>2024</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>692.1990559895833</v>
+        <v>511.7842850343529</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>26359752001.57601</v>
+        <v>28881493897.42368</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>52</v>
       </c>
       <c r="L58" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3673,28 +3673,28 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>5281538</v>
+        <v>36361859</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
         <v>0.222</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>20285.2272897377</v>
+        <v>3161.70010632875</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>2026</v>
@@ -3703,10 +3703,10 @@
         <v>2024</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>4733.219700938796</v>
+        <v>790.4250265821875</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>24998679712.85689</v>
+        <v>28741323366.65275</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>53</v>
@@ -3732,28 +3732,28 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>18135478</v>
+        <v>18406359</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>6874.705739766</v>
+        <v>6150.02571438505</v>
       </c>
       <c r="G60" s="8" t="n">
         <v>2026</v>
@@ -3762,16 +3762,16 @@
         <v>2024</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>1374.9411479532</v>
+        <v>1537.506428596263</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>24935214940</v>
+        <v>28299895289.55067</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>54</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3791,28 +3791,28 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>56432944</v>
+        <v>5281538</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>2132.43452097647</v>
+        <v>20285.2272897377</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>2026</v>
@@ -3821,16 +3821,16 @@
         <v>2024</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>426.4869041952941</v>
+        <v>5071.306822434425</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>24067911581.18639</v>
+        <v>26784299692.34667</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>55</v>
       </c>
       <c r="L61" s="10" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         <v>2024</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>1952.816140316867</v>
+        <v>2343.37936838024</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>20884745672.34014</v>
+        <v>25061694806.80815</v>
       </c>
       <c r="K62" s="10" t="n">
         <v>56</v>
@@ -3939,10 +3939,10 @@
         <v>2024</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>1812.610307384866</v>
+        <v>2175.13236886184</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>20713707606.42808</v>
+        <v>24856449127.7137</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>57</v>
@@ -3998,10 +3998,10 @@
         <v>2024</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>533.174889553506</v>
+        <v>639.8098674642073</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>20199783356.21581</v>
+        <v>24239740027.45897</v>
       </c>
       <c r="K64" s="10" t="n">
         <v>58</v>
@@ -4057,10 +4057,10 @@
         <v>2024</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>903.113574645464</v>
+        <v>1083.736289574557</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>19792637101.92999</v>
+        <v>23751164522.31599</v>
       </c>
       <c r="K65" s="10" t="n">
         <v>59</v>
@@ -4086,16 +4086,16 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>9132629</v>
+        <v>6441421</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>8317.633999137919</v>
+        <v>17596.0173663521</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>2026</v>
@@ -4116,16 +4116,16 @@
         <v>2024</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>2079.40849978448</v>
+        <v>3519.203473270421</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>18990466367.97823</v>
+        <v>22668671155.99702</v>
       </c>
       <c r="K66" s="10" t="n">
         <v>60</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4145,16 +4145,16 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>6441421</v>
+        <v>5422069</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.444</v>
+        <v>0.556</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>17596.0173663521</v>
+        <v>25992.6748502048</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>2026</v>
@@ -4175,16 +4175,16 @@
         <v>2024</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>2932.669561058683</v>
+        <v>4158.827976032767</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>18890559296.66418</v>
+        <v>22549452245.18001</v>
       </c>
       <c r="K67" s="10" t="n">
         <v>61</v>
       </c>
       <c r="L67" s="10" t="n">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4204,28 +4204,28 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>5422069</v>
+        <v>31934230</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>25992.6748502048</v>
+        <v>2727.8935220697</v>
       </c>
       <c r="G68" s="8" t="n">
         <v>2026</v>
@@ -4234,16 +4234,16 @@
         <v>2024</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>3465.689980027306</v>
+        <v>654.6944452967281</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>18791210204.31668</v>
+        <v>20907162995.82813</v>
       </c>
       <c r="K68" s="10" t="n">
         <v>62</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4263,28 +4263,28 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>10202830</v>
+        <v>9132629</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7283.8499076179</v>
+        <v>8317.633999137919</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>2026</v>
@@ -4293,10 +4293,10 @@
         <v>2024</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>1820.962476904475</v>
+        <v>2079.40849978448</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>18578970588.23528</v>
+        <v>18990466367.97823</v>
       </c>
       <c r="K69" s="10" t="n">
         <v>63</v>
@@ -4322,28 +4322,28 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>54500091</v>
+        <v>10202830</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>MMR</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>1359.05001560107</v>
+        <v>7283.8499076179</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>2026</v>
@@ -4352,10 +4352,10 @@
         <v>2024</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>339.7625039002675</v>
+        <v>1820.962476904475</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>18517087380.95243</v>
+        <v>18578970588.23528</v>
       </c>
       <c r="K70" s="10" t="n">
         <v>64</v>
@@ -4381,28 +4381,28 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>109276265</v>
+        <v>54500091</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>MMR</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>649.383338556725</v>
+        <v>1359.05001560107</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>2026</v>
@@ -4411,16 +4411,16 @@
         <v>2024</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>162.3458346391812</v>
+        <v>339.7625039002675</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>17740546447.67735</v>
+        <v>18517087380.95243</v>
       </c>
       <c r="K71" s="10" t="n">
         <v>65</v>
       </c>
       <c r="L71" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4440,28 +4440,28 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>31934230</v>
+        <v>6586476</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>2727.8935220697</v>
+        <v>13679.2065983557</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>2026</v>
@@ -4470,16 +4470,16 @@
         <v>2024</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>545.57870441394</v>
+        <v>2735.84131967114</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>17422635829.85678</v>
+        <v>18019553191.82229</v>
       </c>
       <c r="K72" s="10" t="n">
         <v>66</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4499,28 +4499,28 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>6586476</v>
+        <v>109276265</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>13679.2065983557</v>
+        <v>649.383338556725</v>
       </c>
       <c r="G73" s="8" t="n">
         <v>2026</v>
@@ -4529,16 +4529,16 @@
         <v>2024</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>2279.867766392616</v>
+        <v>162.3458346391812</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>15016294326.51857</v>
+        <v>17740546447.67735</v>
       </c>
       <c r="K73" s="10" t="n">
         <v>67</v>
       </c>
       <c r="L73" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
         <v>2024</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>197.7861531575517</v>
+        <v>237.343383789062</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>13560249712.90779</v>
+        <v>16272299655.48935</v>
       </c>
       <c r="K74" s="10" t="n">
         <v>68</v>
@@ -4617,28 +4617,28 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>50015092</v>
+        <v>10905028</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0.111</v>
+        <v>0.889</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>1077.91278452817</v>
+        <v>31823.3078290564</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>2026</v>
@@ -4647,16 +4647,16 @@
         <v>2024</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>269.4781961320425</v>
+        <v>1272.932313162257</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>13477976771.53815</v>
+        <v>13881362517.13918</v>
       </c>
       <c r="K75" s="10" t="n">
         <v>69</v>
       </c>
       <c r="L75" s="10" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
@@ -4676,28 +4676,28 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>29123744</v>
+        <v>4515577</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>1830.00833684727</v>
+        <v>19161.2188501596</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>2026</v>
@@ -4706,16 +4706,16 @@
         <v>2024</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>457.5020842118175</v>
+        <v>3065.795016025535</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>13324173580.05141</v>
+        <v>13843833461.07954</v>
       </c>
       <c r="K76" s="10" t="n">
         <v>70</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4735,28 +4735,28 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>7494498</v>
+        <v>12413315</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>6856.65802730208</v>
+        <v>4421.16609889999</v>
       </c>
       <c r="G77" s="8" t="n">
         <v>2026</v>
@@ -4765,16 +4765,16 @@
         <v>2024</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>1714.16450682552</v>
+        <v>1105.291524724998</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>12846802468.07485</v>
+        <v>13720331863.24168</v>
       </c>
       <c r="K77" s="10" t="n">
         <v>71</v>
       </c>
       <c r="L77" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4794,28 +4794,28 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>12413315</v>
+        <v>50015092</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.222</v>
+        <v>0.111</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>4421.16609889999</v>
+        <v>1077.91278452817</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>2026</v>
@@ -4824,16 +4824,16 @@
         <v>2024</v>
       </c>
       <c r="I78" s="7" t="n">
-        <v>1031.605423076664</v>
+        <v>269.4781961320425</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>12805643072.35891</v>
+        <v>13477976771.53815</v>
       </c>
       <c r="K78" s="10" t="n">
         <v>72</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4853,28 +4853,28 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>50448963</v>
+        <v>29123744</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>984.607666015625</v>
+        <v>1830.00833684727</v>
       </c>
       <c r="G79" s="8" t="n">
         <v>2026</v>
@@ -4883,16 +4883,16 @@
         <v>2024</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>246.1519165039062</v>
+        <v>457.5020842118175</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>12418108928.08466</v>
+        <v>13324173580.05141</v>
       </c>
       <c r="K79" s="10" t="n">
         <v>73</v>
       </c>
       <c r="L79" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4912,28 +4912,28 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>7381023</v>
+        <v>19764771</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>6569.16408678648</v>
+        <v>16709.8893972307</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2026</v>
@@ -4942,16 +4942,16 @@
         <v>2024</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>1642.29102169662</v>
+        <v>668.3955758892283</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>12121787803.83625</v>
+        <v>13210685494.86372</v>
       </c>
       <c r="K80" s="10" t="n">
         <v>74</v>
       </c>
       <c r="L80" s="10" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4971,28 +4971,28 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>1588670</v>
+        <v>34427414</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>29653.5682731534</v>
+        <v>2390.77237652715</v>
       </c>
       <c r="G81" s="8" t="n">
         <v>2026</v>
@@ -5001,16 +5001,16 @@
         <v>2024</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>7413.39206828835</v>
+        <v>382.5235802443439</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>11777433577.12765</v>
+        <v>13169297661.83425</v>
       </c>
       <c r="K81" s="10" t="n">
         <v>75</v>
       </c>
       <c r="L81" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5030,28 +5030,28 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>17638801</v>
+        <v>7494498</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>2627.87969756224</v>
+        <v>6856.65802730208</v>
       </c>
       <c r="G82" s="8" t="n">
         <v>2026</v>
@@ -5060,10 +5060,10 @@
         <v>2024</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>656.96992439056</v>
+        <v>1714.16450682552</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>11588161759.31013</v>
+        <v>12846802468.07485</v>
       </c>
       <c r="K82" s="10" t="n">
         <v>76</v>
@@ -5089,28 +5089,28 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>10905028</v>
+        <v>11552876</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0.889</v>
+        <v>0.333</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>31823.3078290564</v>
+        <v>4618.09592498567</v>
       </c>
       <c r="G83" s="8" t="n">
         <v>2026</v>
@@ -5119,16 +5119,16 @@
         <v>2024</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>1060.776927635214</v>
+        <v>1108.343021996561</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>11567802097.61598</v>
+        <v>12804549498.59154</v>
       </c>
       <c r="K83" s="10" t="n">
         <v>77</v>
       </c>
       <c r="L83" s="10" t="n">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
@@ -5148,28 +5148,28 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>4515577</v>
+        <v>50448963</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>19161.2188501596</v>
+        <v>984.607666015625</v>
       </c>
       <c r="G84" s="8" t="n">
         <v>2026</v>
@@ -5178,16 +5178,16 @@
         <v>2024</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>2554.82918002128</v>
+        <v>246.1519165039062</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>11536527884.23295</v>
+        <v>12418108928.08466</v>
       </c>
       <c r="K84" s="10" t="n">
         <v>78</v>
       </c>
       <c r="L84" s="10" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5207,28 +5207,28 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>19764771</v>
+        <v>7381023</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>16709.8893972307</v>
+        <v>6569.16408678648</v>
       </c>
       <c r="G85" s="8" t="n">
         <v>2026</v>
@@ -5237,16 +5237,16 @@
         <v>2024</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>556.9963132410236</v>
+        <v>1642.29102169662</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>11008904579.0531</v>
+        <v>12121787803.83625</v>
       </c>
       <c r="K85" s="10" t="n">
         <v>79</v>
       </c>
       <c r="L85" s="10" t="n">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5266,28 +5266,28 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>34427414</v>
+        <v>1588670</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>2390.77237652715</v>
+        <v>29653.5682731534</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>2026</v>
@@ -5296,16 +5296,16 @@
         <v>2024</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>318.76965020362</v>
+        <v>7413.39206828835</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>10974414718.19521</v>
+        <v>11777433577.12765</v>
       </c>
       <c r="K86" s="10" t="n">
         <v>80</v>
       </c>
       <c r="L86" s="10" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5325,28 +5325,28 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>11552876</v>
+        <v>17638801</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>4618.09592498567</v>
+        <v>2627.87969756224</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>2026</v>
@@ -5355,16 +5355,16 @@
         <v>2024</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>923.619184997134</v>
+        <v>656.96992439056</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>10670457915.49295</v>
+        <v>11588161759.31013</v>
       </c>
       <c r="K87" s="10" t="n">
         <v>81</v>
       </c>
       <c r="L87" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5384,28 +5384,28 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>16634373</v>
+        <v>3866200</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.111</v>
+        <v>0.667</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>2497.20332208763</v>
+        <v>24050.4397933135</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>2026</v>
@@ -5414,16 +5414,16 @@
         <v>2024</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>624.3008305219075</v>
+        <v>2886.05277519762</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>10384852879.11119</v>
+        <v>11158057239.46904</v>
       </c>
       <c r="K88" s="10" t="n">
         <v>82</v>
       </c>
       <c r="L88" s="10" t="n">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5443,28 +5443,28 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>3866200</v>
+        <v>6929153</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>24050.4397933135</v>
+        <v>6416.09708970845</v>
       </c>
       <c r="G89" s="8" t="n">
         <v>2026</v>
@@ -5473,16 +5473,16 @@
         <v>2024</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>2405.043979331349</v>
+        <v>1539.863301530028</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>9298381032.890863</v>
+        <v>10669948415.3867</v>
       </c>
       <c r="K89" s="10" t="n">
         <v>83</v>
       </c>
       <c r="L89" s="10" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5502,28 +5502,28 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>6929153</v>
+        <v>5287500</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.333</v>
+        <v>0.889</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>6416.09708970845</v>
+        <v>49205.1792146792</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>2026</v>
@@ -5532,16 +5532,16 @@
         <v>2024</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>1283.21941794169</v>
+        <v>1968.207168587169</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>8891623679.488916</v>
+        <v>10406895403.90466</v>
       </c>
       <c r="K90" s="10" t="n">
         <v>84</v>
       </c>
       <c r="L90" s="10" t="n">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5561,28 +5561,28 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>6338193</v>
+        <v>16634373</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>5579.65969165029</v>
+        <v>2497.20332208763</v>
       </c>
       <c r="G91" s="8" t="n">
         <v>2026</v>
@@ -5591,16 +5591,16 @@
         <v>2024</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>1394.914922912573</v>
+        <v>624.3008305219075</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>8841240000.000008</v>
+        <v>10384852879.11119</v>
       </c>
       <c r="K91" s="10" t="n">
         <v>85</v>
       </c>
       <c r="L91" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5620,28 +5620,28 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>5287500</v>
+        <v>29651054</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.889</v>
+        <v>0.333</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>49205.1792146792</v>
+        <v>1447.31004458428</v>
       </c>
       <c r="G92" s="8" t="n">
         <v>2026</v>
@@ -5650,16 +5650,16 @@
         <v>2024</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>1640.172640489307</v>
+        <v>347.3544107002272</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>8672412836.587212</v>
+        <v>10299424388.81062</v>
       </c>
       <c r="K92" s="10" t="n">
         <v>86</v>
       </c>
       <c r="L92" s="10" t="n">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5679,28 +5679,28 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>10825703</v>
+        <v>12277109</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>3426.43483328923</v>
+        <v>4181.13789301228</v>
       </c>
       <c r="G93" s="8" t="n">
         <v>2026</v>
@@ -5709,16 +5709,16 @@
         <v>2024</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>799.5014611008204</v>
+        <v>836.2275786024561</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>8655165365.943535</v>
+        <v>10266457131.30842</v>
       </c>
       <c r="K93" s="10" t="n">
         <v>87</v>
       </c>
       <c r="L93" s="10" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5738,28 +5738,28 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>29651054</v>
+        <v>2888278</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>1447.31004458428</v>
+        <v>29384.0189598663</v>
       </c>
       <c r="G94" s="8" t="n">
         <v>2026</v>
@@ -5768,16 +5768,16 @@
         <v>2024</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>289.462008916856</v>
+        <v>3526.082275183956</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>8582853657.342179</v>
+        <v>10184305861.60377</v>
       </c>
       <c r="K94" s="10" t="n">
         <v>88</v>
       </c>
       <c r="L94" s="10" t="n">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5797,28 +5797,28 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>12277109</v>
+        <v>10825703</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>4181.13789301228</v>
+        <v>3426.43483328923</v>
       </c>
       <c r="G95" s="8" t="n">
         <v>2026</v>
@@ -5827,16 +5827,16 @@
         <v>2024</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>696.8563155020466</v>
+        <v>856.6087083223075</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>8555380942.757016</v>
+        <v>9273391463.510929</v>
       </c>
       <c r="K95" s="10" t="n">
         <v>89</v>
       </c>
       <c r="L95" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5856,28 +5856,28 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>2888278</v>
+        <v>6338193</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>29384.0189598663</v>
+        <v>5579.65969165029</v>
       </c>
       <c r="G96" s="8" t="n">
         <v>2026</v>
@@ -5886,16 +5886,16 @@
         <v>2024</v>
       </c>
       <c r="I96" s="7" t="n">
-        <v>2938.401895986629</v>
+        <v>1394.914922912573</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>8486921551.33647</v>
+        <v>8841240000.000008</v>
       </c>
       <c r="K96" s="10" t="n">
         <v>90</v>
       </c>
       <c r="L96" s="10" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5945,16 +5945,16 @@
         <v>2024</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>3430.103186865939</v>
+        <v>4116.123824239128</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>7297201519.738598</v>
+        <v>8756641823.686321</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>91</v>
       </c>
       <c r="L97" s="10" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -6004,10 +6004,10 @@
         <v>2024</v>
       </c>
       <c r="I98" s="7" t="n">
-        <v>601.3411289578461</v>
+        <v>721.6093547494153</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>6360085653.104917</v>
+        <v>7632102783.7259</v>
       </c>
       <c r="K98" s="10" t="n">
         <v>92</v>
@@ -6033,28 +6033,28 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>14754785</v>
+        <v>3699557</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>1694.95375862193</v>
+        <v>9241.491223137131</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>2026</v>
@@ -6063,16 +6063,16 @@
         <v>2024</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>423.7384396554825</v>
+        <v>1848.298244627426</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>6252169573.352118</v>
+        <v>6837884708.999107</v>
       </c>
       <c r="K99" s="10" t="n">
         <v>93</v>
       </c>
       <c r="L99" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -6092,28 +6092,28 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>11772557</v>
+        <v>18501984</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>2142.62330526788</v>
+        <v>1773.21829923448</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>2026</v>
@@ -6122,16 +6122,16 @@
         <v>2024</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>499.9454378958387</v>
+        <v>354.643659846896</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>5885636164.518721</v>
+        <v>6561611320.188712</v>
       </c>
       <c r="K100" s="10" t="n">
         <v>94</v>
       </c>
       <c r="L100" s="10" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6151,16 +6151,16 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>23548781</v>
+        <v>24478595</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>981.992649769081</v>
+        <v>1094.61949265799</v>
       </c>
       <c r="G101" s="8" t="n">
         <v>2026</v>
@@ -6181,16 +6181,16 @@
         <v>2024</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>245.4981624422703</v>
+        <v>262.7086782379176</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>5781182463.255447</v>
+        <v>6430739337.571298</v>
       </c>
       <c r="K101" s="10" t="n">
         <v>95</v>
       </c>
       <c r="L101" s="10" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6210,28 +6210,28 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>3699557</v>
+        <v>11772557</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>9241.491223137131</v>
+        <v>2142.62330526788</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>2026</v>
@@ -6240,16 +6240,16 @@
         <v>2024</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>1540.248537189522</v>
+        <v>535.65582631697</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>5698237257.499256</v>
+        <v>6306038747.698629</v>
       </c>
       <c r="K102" s="10" t="n">
         <v>96</v>
       </c>
       <c r="L102" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6269,28 +6269,28 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>34631766</v>
+        <v>1358282</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>656.776824637306</v>
+        <v>38674.29296875</v>
       </c>
       <c r="G103" s="8" t="n">
         <v>2026</v>
@@ -6299,16 +6299,16 @@
         <v>2024</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>164.1942061593265</v>
+        <v>4640.91515625</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>5686335326.265554</v>
+        <v>6303671520.261562</v>
       </c>
       <c r="K103" s="10" t="n">
         <v>97</v>
       </c>
       <c r="L103" s="10" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O103" s="6" t="inlineStr">
@@ -6328,16 +6328,16 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>18501984</v>
+        <v>14754785</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>1773.21829923448</v>
+        <v>1694.95375862193</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>2026</v>
@@ -6358,16 +6358,16 @@
         <v>2024</v>
       </c>
       <c r="I104" s="7" t="n">
-        <v>295.5363832057466</v>
+        <v>423.7384396554825</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>5468009433.490593</v>
+        <v>6252169573.352118</v>
       </c>
       <c r="K104" s="10" t="n">
         <v>98</v>
       </c>
       <c r="L104" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -6387,28 +6387,28 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>24478595</v>
+        <v>1368333</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>1094.61949265799</v>
+        <v>18733.4110406494</v>
       </c>
       <c r="G105" s="8" t="n">
         <v>2026</v>
@@ -6417,10 +6417,10 @@
         <v>2024</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>218.923898531598</v>
+        <v>4496.018649755856</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>5358949447.976082</v>
+        <v>6152050687.07638</v>
       </c>
       <c r="K105" s="10" t="n">
         <v>99</v>
@@ -6446,28 +6446,28 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>1358282</v>
+        <v>21314956</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>38674.29296875</v>
+        <v>1187.10943350064</v>
       </c>
       <c r="G106" s="8" t="n">
         <v>2026</v>
@@ -6476,16 +6476,16 @@
         <v>2024</v>
       </c>
       <c r="I106" s="7" t="n">
-        <v>3867.429296874999</v>
+        <v>284.9062640401536</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>5253059600.217968</v>
+        <v>6072764482.140257</v>
       </c>
       <c r="K106" s="10" t="n">
         <v>100</v>
       </c>
       <c r="L106" s="10" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O106" s="6" t="inlineStr">
@@ -6505,28 +6505,28 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>1368333</v>
+        <v>3164253</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>18733.4110406494</v>
+        <v>9358.78768951134</v>
       </c>
       <c r="G107" s="8" t="n">
         <v>2026</v>
@@ -6535,16 +6535,16 @@
         <v>2024</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>3746.68220812988</v>
+        <v>1871.757537902268</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>5126708905.896983</v>
+        <v>5922714404.579866</v>
       </c>
       <c r="K107" s="10" t="n">
         <v>101</v>
       </c>
       <c r="L107" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
@@ -6564,28 +6564,28 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>21314956</v>
+        <v>23548781</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.333</v>
+        <v>0.111</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>1187.10943350064</v>
+        <v>981.992649769081</v>
       </c>
       <c r="G108" s="8" t="n">
         <v>2026</v>
@@ -6594,16 +6594,16 @@
         <v>2024</v>
       </c>
       <c r="I108" s="7" t="n">
-        <v>237.421886700128</v>
+        <v>245.4981624422703</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>5060637068.450214</v>
+        <v>5781182463.255447</v>
       </c>
       <c r="K108" s="10" t="n">
         <v>102</v>
       </c>
       <c r="L108" s="10" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -6623,28 +6623,28 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>3164253</v>
+        <v>34631766</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>9358.78768951134</v>
+        <v>656.776824637306</v>
       </c>
       <c r="G109" s="8" t="n">
         <v>2026</v>
@@ -6653,16 +6653,16 @@
         <v>2024</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>1559.79794825189</v>
+        <v>164.1942061593265</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>4935595337.149887</v>
+        <v>5686335326.265554</v>
       </c>
       <c r="K109" s="10" t="n">
         <v>103</v>
       </c>
       <c r="L109" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -6682,28 +6682,28 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>6916140</v>
+        <v>2377128</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>2847.53966339498</v>
+        <v>11377.7757431099</v>
       </c>
       <c r="G110" s="8" t="n">
         <v>2026</v>
@@ -6712,16 +6712,16 @@
         <v>2024</v>
       </c>
       <c r="I110" s="7" t="n">
-        <v>711.884915848745</v>
+        <v>2275.55514862198</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>4923495741.898139</v>
+        <v>5409285859.33347</v>
       </c>
       <c r="K110" s="10" t="n">
         <v>104</v>
       </c>
       <c r="L110" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
@@ -6741,28 +6741,28 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>20299123</v>
+        <v>3033500</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>961.55975562506</v>
+        <v>8556.21406956719</v>
       </c>
       <c r="G111" s="8" t="n">
         <v>2026</v>
@@ -6771,16 +6771,16 @@
         <v>2024</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>240.389938906265</v>
+        <v>1711.242813913438</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>4879704937.820759</v>
+        <v>5191055076.006414</v>
       </c>
       <c r="K111" s="10" t="n">
         <v>105</v>
       </c>
       <c r="L111" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
@@ -6800,28 +6800,28 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>2377128</v>
+        <v>831087</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
         <v>0.444</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>11377.7757431099</v>
+        <v>29675.2443873316</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>2026</v>
@@ -6830,10 +6830,10 @@
         <v>2024</v>
       </c>
       <c r="I112" s="7" t="n">
-        <v>1896.295957184983</v>
+        <v>5935.048877466321</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>4507738216.111225</v>
+        <v>4932541966.426852</v>
       </c>
       <c r="K112" s="10" t="n">
         <v>106</v>
@@ -6859,28 +6859,28 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>42647492</v>
+        <v>6916140</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>413.757894705303</v>
+        <v>2847.53966339498</v>
       </c>
       <c r="G113" s="8" t="n">
         <v>2026</v>
@@ -6889,10 +6889,10 @@
         <v>2024</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>103.4394736763257</v>
+        <v>711.884915848745</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>4411434126.095313</v>
+        <v>4923495741.898139</v>
       </c>
       <c r="K113" s="10" t="n">
         <v>107</v>
@@ -6918,28 +6918,28 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>3033500</v>
+        <v>20299123</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>8556.21406956719</v>
+        <v>961.55975562506</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>2026</v>
@@ -6948,16 +6948,16 @@
         <v>2024</v>
       </c>
       <c r="I114" s="7" t="n">
-        <v>1426.035678261198</v>
+        <v>240.389938906265</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>4325879230.005344</v>
+        <v>4879704937.820759</v>
       </c>
       <c r="K114" s="10" t="n">
         <v>108</v>
       </c>
       <c r="L114" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
@@ -6977,28 +6977,28 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>7769819</v>
+        <v>5805962</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>2123.97909415109</v>
+        <v>3477.72489842684</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>2026</v>
@@ -7007,16 +7007,16 @@
         <v>2024</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>530.9947735377725</v>
+        <v>834.6539756224416</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>4125733280.334482</v>
+        <v>4845969265.612823</v>
       </c>
       <c r="K115" s="10" t="n">
         <v>109</v>
       </c>
       <c r="L115" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
@@ -7036,28 +7036,28 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>831087</v>
+        <v>27032412</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>29675.2443873316</v>
+        <v>735.270255787226</v>
       </c>
       <c r="G116" s="8" t="n">
         <v>2026</v>
@@ -7066,16 +7066,16 @@
         <v>2024</v>
       </c>
       <c r="I116" s="7" t="n">
-        <v>4945.874064555266</v>
+        <v>176.4648613889343</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>4110451638.689043</v>
+        <v>4770270836.588563</v>
       </c>
       <c r="K116" s="10" t="n">
         <v>110</v>
       </c>
       <c r="L116" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
@@ -7095,28 +7095,28 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>7221868</v>
+        <v>3524788</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>2420.18542283831</v>
+        <v>6750.6301157724</v>
       </c>
       <c r="G117" s="8" t="n">
         <v>2026</v>
@@ -7125,16 +7125,16 @@
         <v>2024</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>564.7099319956056</v>
+        <v>1350.12602315448</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>4078260587.161241</v>
+        <v>4758908004.902634</v>
       </c>
       <c r="K117" s="10" t="n">
         <v>111</v>
       </c>
       <c r="L117" s="10" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
@@ -7154,28 +7154,28 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>31964956</v>
+        <v>2521139</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>544.987501003384</v>
+        <v>7695.75319445165</v>
       </c>
       <c r="G118" s="8" t="n">
         <v>2026</v>
@@ -7184,16 +7184,16 @@
         <v>2024</v>
       </c>
       <c r="I118" s="7" t="n">
-        <v>127.1637502341229</v>
+        <v>1846.980766668396</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>4064783681.028729</v>
+        <v>4656495243.097593</v>
       </c>
       <c r="K118" s="10" t="n">
         <v>112</v>
       </c>
       <c r="L118" s="10" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
@@ -7213,28 +7213,28 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>5805962</v>
+        <v>42647492</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>3477.72489842684</v>
+        <v>413.757894705303</v>
       </c>
       <c r="G119" s="8" t="n">
         <v>2026</v>
@@ -7243,16 +7243,16 @@
         <v>2024</v>
       </c>
       <c r="I119" s="7" t="n">
-        <v>695.544979685368</v>
+        <v>103.4394736763257</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>4038307721.344019</v>
+        <v>4411434126.095313</v>
       </c>
       <c r="K119" s="10" t="n">
         <v>113</v>
       </c>
       <c r="L119" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
@@ -7272,28 +7272,28 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>27032412</v>
+        <v>2839175</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>735.270255787226</v>
+        <v>7753.8006955432</v>
       </c>
       <c r="G120" s="8" t="n">
         <v>2026</v>
@@ -7302,16 +7302,16 @@
         <v>2024</v>
       </c>
       <c r="I120" s="7" t="n">
-        <v>147.0540511574452</v>
+        <v>1550.76013910864</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>3975225697.157135</v>
+        <v>4402879417.953773</v>
       </c>
       <c r="K120" s="10" t="n">
         <v>114</v>
       </c>
       <c r="L120" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
@@ -7331,28 +7331,28 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>3524788</v>
+        <v>7221868</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>6750.6301157724</v>
+        <v>2420.18542283831</v>
       </c>
       <c r="G121" s="8" t="n">
         <v>2026</v>
@@ -7361,16 +7361,16 @@
         <v>2024</v>
       </c>
       <c r="I121" s="7" t="n">
-        <v>1125.1050192954</v>
+        <v>605.0463557095775</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>3965756670.752194</v>
+        <v>4369564914.815615</v>
       </c>
       <c r="K121" s="10" t="n">
         <v>115</v>
       </c>
       <c r="L121" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M121" s="6" t="inlineStr">
         <is>
@@ -7390,28 +7390,28 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>401283</v>
+        <v>31964956</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>39455.4466548546</v>
+        <v>544.987501003384</v>
       </c>
       <c r="G122" s="8" t="n">
         <v>2026</v>
@@ -7420,16 +7420,16 @@
         <v>2024</v>
       </c>
       <c r="I122" s="7" t="n">
-        <v>9863.861663713649</v>
+        <v>136.246875250846</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>3958200000.000004</v>
+        <v>4355125372.530781</v>
       </c>
       <c r="K122" s="10" t="n">
         <v>116</v>
       </c>
       <c r="L122" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M122" s="6" t="inlineStr">
         <is>
@@ -7449,28 +7449,28 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>6332961</v>
+        <v>14462724</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Congo Republic</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>2482.2489948456</v>
+        <v>1485.38018885134</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>2026</v>
@@ -7479,16 +7479,16 @@
         <v>2024</v>
       </c>
       <c r="I123" s="7" t="n">
-        <v>620.5622487114</v>
+        <v>297.076037770268</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>3929996519.161596</v>
+        <v>4296528741.284962</v>
       </c>
       <c r="K123" s="10" t="n">
         <v>117</v>
       </c>
       <c r="L123" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
@@ -7508,28 +7508,28 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>2521139</v>
+        <v>2538952</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>7695.75319445165</v>
+        <v>8230.043114511511</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>2026</v>
@@ -7538,16 +7538,16 @@
         <v>2024</v>
       </c>
       <c r="I124" s="7" t="n">
-        <v>1539.15063889033</v>
+        <v>1646.008622902302</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>3880412702.581328</v>
+        <v>4179136885.135046</v>
       </c>
       <c r="K124" s="10" t="n">
         <v>118</v>
       </c>
       <c r="L124" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M124" s="6" t="inlineStr">
         <is>
@@ -7567,16 +7567,16 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>462721</v>
+        <v>7769819</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>33153.4738913513</v>
+        <v>2123.97909415109</v>
       </c>
       <c r="G125" s="8" t="n">
         <v>2026</v>
@@ -7597,10 +7597,10 @@
         <v>2024</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>8288.368472837825</v>
+        <v>530.9947735377725</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>3835202148.119991</v>
+        <v>4125733280.334482</v>
       </c>
       <c r="K125" s="10" t="n">
         <v>119</v>
@@ -7626,28 +7626,28 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>2839175</v>
+        <v>1824359</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>7753.8006955432</v>
+        <v>9291.85661671864</v>
       </c>
       <c r="G126" s="8" t="n">
         <v>2026</v>
@@ -7656,16 +7656,16 @@
         <v>2024</v>
       </c>
       <c r="I126" s="7" t="n">
-        <v>1292.300115923867</v>
+        <v>2230.045588012474</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>3669066181.628144</v>
+        <v>4068403738.900848</v>
       </c>
       <c r="K126" s="10" t="n">
         <v>120</v>
       </c>
       <c r="L126" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
@@ -7685,28 +7685,28 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>14462724</v>
+        <v>401283</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>1485.38018885134</v>
+        <v>39455.4466548546</v>
       </c>
       <c r="G127" s="8" t="n">
         <v>2026</v>
@@ -7715,16 +7715,16 @@
         <v>2024</v>
       </c>
       <c r="I127" s="7" t="n">
-        <v>247.5633648085567</v>
+        <v>9863.861663713649</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>3580440617.737468</v>
+        <v>3958200000.000004</v>
       </c>
       <c r="K127" s="10" t="n">
         <v>121</v>
       </c>
       <c r="L127" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
@@ -7744,28 +7744,28 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>14256567</v>
+        <v>6332961</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Congo Republic</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>999.65456165547</v>
+        <v>2482.2489948456</v>
       </c>
       <c r="G128" s="8" t="n">
         <v>2026</v>
@@ -7774,10 +7774,10 @@
         <v>2024</v>
       </c>
       <c r="I128" s="7" t="n">
-        <v>249.9136404138675</v>
+        <v>620.5622487114</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>3562910558.77421</v>
+        <v>3929996519.161596</v>
       </c>
       <c r="K128" s="10" t="n">
         <v>122</v>
@@ -7803,28 +7803,28 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>10590927</v>
+        <v>462721</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>1341.20229027672</v>
+        <v>33153.4738913513</v>
       </c>
       <c r="G129" s="8" t="n">
         <v>2026</v>
@@ -7833,10 +7833,10 @@
         <v>2024</v>
       </c>
       <c r="I129" s="7" t="n">
-        <v>335.30057256918</v>
+        <v>8288.368472837825</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>3551143887.138388</v>
+        <v>3835202148.119991</v>
       </c>
       <c r="K129" s="10" t="n">
         <v>123</v>
@@ -7862,28 +7862,28 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>1245779</v>
+        <v>5129910</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.222</v>
+        <v>0.889</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>11990.7798944837</v>
+        <v>18587.1532203482</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>2026</v>
@@ -7892,16 +7892,16 @@
         <v>2024</v>
       </c>
       <c r="I130" s="7" t="n">
-        <v>2797.848642046197</v>
+        <v>743.4861288139282</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>3485501083.439669</v>
+        <v>3814016927.063859</v>
       </c>
       <c r="K130" s="10" t="n">
         <v>124</v>
       </c>
       <c r="L130" s="10" t="n">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
@@ -7921,28 +7921,28 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>2538952</v>
+        <v>1245779</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>8230.043114511511</v>
+        <v>11990.7798944837</v>
       </c>
       <c r="G131" s="8" t="n">
         <v>2026</v>
@@ -7951,16 +7951,16 @@
         <v>2024</v>
       </c>
       <c r="I131" s="7" t="n">
-        <v>1371.673852418585</v>
+        <v>2997.694973620925</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>3482614070.945871</v>
+        <v>3734465446.542502</v>
       </c>
       <c r="K131" s="10" t="n">
         <v>125</v>
       </c>
       <c r="L131" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
@@ -7980,28 +7980,28 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>1824359</v>
+        <v>14256567</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>9291.85661671864</v>
+        <v>999.65456165547</v>
       </c>
       <c r="G132" s="8" t="n">
         <v>2026</v>
@@ -8010,16 +8010,16 @@
         <v>2024</v>
       </c>
       <c r="I132" s="7" t="n">
-        <v>1858.371323343728</v>
+        <v>249.9136404138675</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>3390336449.084041</v>
+        <v>3562910558.77421</v>
       </c>
       <c r="K132" s="10" t="n">
         <v>126</v>
       </c>
       <c r="L132" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
@@ -8039,28 +8039,28 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>1892516</v>
+        <v>10590927</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>6745.40013244916</v>
+        <v>1341.20229027672</v>
       </c>
       <c r="G133" s="8" t="n">
         <v>2026</v>
@@ -8069,10 +8069,10 @@
         <v>2024</v>
       </c>
       <c r="I133" s="7" t="n">
-        <v>1686.35003311229</v>
+        <v>335.30057256918</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>3191444419.265539</v>
+        <v>3551143887.138388</v>
       </c>
       <c r="K133" s="10" t="n">
         <v>127</v>
@@ -8098,28 +8098,28 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>5129910</v>
+        <v>3386588</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
         <v>0.889</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>18587.1532203482</v>
+        <v>23906.5133029408</v>
       </c>
       <c r="G134" s="8" t="n">
         <v>2026</v>
@@ -8128,10 +8128,10 @@
         <v>2024</v>
       </c>
       <c r="I134" s="7" t="n">
-        <v>619.5717740116069</v>
+        <v>956.2605321176324</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>3178347439.219882</v>
+        <v>3238460442.943188</v>
       </c>
       <c r="K134" s="10" t="n">
         <v>128</v>
@@ -8157,28 +8157,28 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>19009151</v>
+        <v>1892516</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>629.538899449007</v>
+        <v>6745.40013244916</v>
       </c>
       <c r="G135" s="8" t="n">
         <v>2026</v>
@@ -8187,16 +8187,16 @@
         <v>2024</v>
       </c>
       <c r="I135" s="7" t="n">
-        <v>157.3847248622517</v>
+        <v>1686.35003311229</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>2991749999.999998</v>
+        <v>3191444419.265539</v>
       </c>
       <c r="K135" s="10" t="n">
         <v>129</v>
       </c>
       <c r="L135" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
@@ -8216,28 +8216,28 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
-        <v>38631</v>
+        <v>568847</v>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>288001.433369041</v>
+        <v>43898.5781808597</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>2026</v>
@@ -8246,16 +8246,16 @@
         <v>2024</v>
       </c>
       <c r="I136" s="7" t="n">
-        <v>72000.35834226025</v>
+        <v>5267.829381703164</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>2781445843.119856</v>
+        <v>2996588940.2937</v>
       </c>
       <c r="K136" s="10" t="n">
         <v>130</v>
       </c>
       <c r="L136" s="10" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
@@ -8275,28 +8275,28 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>3386588</v>
+        <v>19009151</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0.889</v>
+        <v>0.111</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>23906.5133029408</v>
+        <v>629.538899449007</v>
       </c>
       <c r="G137" s="8" t="n">
         <v>2026</v>
@@ -8305,16 +8305,16 @@
         <v>2024</v>
       </c>
       <c r="I137" s="7" t="n">
-        <v>796.8837767646936</v>
+        <v>157.3847248622517</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>2698717035.78599</v>
+        <v>2991749999.999998</v>
       </c>
       <c r="K137" s="10" t="n">
         <v>131</v>
       </c>
       <c r="L137" s="10" t="n">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
@@ -8334,28 +8334,28 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>9515236</v>
+        <v>38631</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>1119.38160509429</v>
+        <v>288001.433369041</v>
       </c>
       <c r="G138" s="8" t="n">
         <v>2026</v>
@@ -8364,10 +8364,10 @@
         <v>2024</v>
       </c>
       <c r="I138" s="7" t="n">
-        <v>279.8454012735725</v>
+        <v>72000.35834226025</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>2662795036.632743</v>
+        <v>2781445843.119856</v>
       </c>
       <c r="K138" s="10" t="n">
         <v>132</v>
@@ -8423,10 +8423,10 @@
         <v>2024</v>
       </c>
       <c r="I139" s="7" t="n">
-        <v>492.3614195224364</v>
+        <v>527.5300923454676</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>2545210660.272185</v>
+        <v>2727011421.720198</v>
       </c>
       <c r="K139" s="10" t="n">
         <v>133</v>
@@ -8452,28 +8452,28 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>568847</v>
+        <v>21655286</v>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>43898.5781808597</v>
+        <v>522.5703936425469</v>
       </c>
       <c r="G140" s="8" t="n">
         <v>2026</v>
@@ -8482,16 +8482,16 @@
         <v>2024</v>
       </c>
       <c r="I140" s="7" t="n">
-        <v>4389.857818085969</v>
+        <v>125.4168944742113</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>2497157450.24475</v>
+        <v>2715938719.070865</v>
       </c>
       <c r="K140" s="10" t="n">
         <v>134</v>
       </c>
       <c r="L140" s="10" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
@@ -8511,28 +8511,28 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>21655286</v>
+        <v>9515236</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>522.5703936425469</v>
+        <v>1119.38160509429</v>
       </c>
       <c r="G141" s="8" t="n">
         <v>2026</v>
@@ -8541,16 +8541,16 @@
         <v>2024</v>
       </c>
       <c r="I141" s="7" t="n">
-        <v>104.5140787285094</v>
+        <v>279.8454012735725</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>2263282265.892387</v>
+        <v>2662795036.632743</v>
       </c>
       <c r="K141" s="10" t="n">
         <v>135</v>
       </c>
       <c r="L141" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
@@ -8570,28 +8570,28 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
-        <v>40450</v>
+        <v>2402306</v>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>206780.590353385</v>
+        <v>7576.19589413326</v>
       </c>
       <c r="G142" s="8" t="n">
         <v>2026</v>
@@ -8600,16 +8600,16 @@
         <v>2024</v>
       </c>
       <c r="I142" s="7" t="n">
-        <v>51695.14758834625</v>
+        <v>909.1435072959912</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>2091068719.948606</v>
+        <v>2184040902.438203</v>
       </c>
       <c r="K142" s="10" t="n">
         <v>136</v>
       </c>
       <c r="L142" s="10" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
@@ -8629,28 +8629,28 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>2402306</v>
+        <v>3030131</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>7576.19589413326</v>
+        <v>4413.12752211572</v>
       </c>
       <c r="G143" s="8" t="n">
         <v>2026</v>
@@ -8659,16 +8659,16 @@
         <v>2024</v>
       </c>
       <c r="I143" s="7" t="n">
-        <v>757.6195894133258</v>
+        <v>706.1004035385151</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>1820034085.365169</v>
+        <v>2139576721.874564</v>
       </c>
       <c r="K143" s="10" t="n">
         <v>137</v>
       </c>
       <c r="L143" s="10" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
@@ -8688,28 +8688,28 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>3030131</v>
+        <v>40450</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>LIE</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F144" s="7" t="n">
-        <v>4413.12752211572</v>
+        <v>206780.590353385</v>
       </c>
       <c r="G144" s="8" t="n">
         <v>2026</v>
@@ -8718,16 +8718,16 @@
         <v>2024</v>
       </c>
       <c r="I144" s="7" t="n">
-        <v>588.4170029487627</v>
+        <v>51695.14758834625</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>1782980601.562137</v>
+        <v>2091068719.948606</v>
       </c>
       <c r="K144" s="10" t="n">
         <v>138</v>
       </c>
       <c r="L144" s="10" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
@@ -8777,10 +8777,10 @@
         <v>2024</v>
       </c>
       <c r="I145" s="7" t="n">
-        <v>2675.87027154448</v>
+        <v>3211.044325853376</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>1412321653.450905</v>
+        <v>1694785984.141086</v>
       </c>
       <c r="K145" s="10" t="n">
         <v>139</v>
@@ -8836,10 +8836,10 @@
         <v>2024</v>
       </c>
       <c r="I146" s="7" t="n">
-        <v>161.3309300835452</v>
+        <v>193.5971161002543</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>1394225447.062459</v>
+        <v>1673070536.474952</v>
       </c>
       <c r="K146" s="10" t="n">
         <v>140</v>
@@ -8865,28 +8865,28 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>1242822</v>
+        <v>386506</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0.111</v>
+        <v>0.889</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>3909.55892378182</v>
+        <v>86040.5309851288</v>
       </c>
       <c r="G147" s="8" t="n">
         <v>2026</v>
@@ -8895,16 +8895,16 @@
         <v>2024</v>
       </c>
       <c r="I147" s="7" t="n">
-        <v>977.389730945455</v>
+        <v>3441.621239405154</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>1214721460.193092</v>
+        <v>1330207258.757528</v>
       </c>
       <c r="K147" s="10" t="n">
         <v>141</v>
       </c>
       <c r="L147" s="10" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
@@ -8924,28 +8924,28 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>386506</v>
+        <v>623525</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.889</v>
+        <v>0.556</v>
       </c>
       <c r="F148" s="7" t="n">
-        <v>86040.5309851288</v>
+        <v>13263.3281277699</v>
       </c>
       <c r="G148" s="8" t="n">
         <v>2026</v>
@@ -8954,16 +8954,16 @@
         <v>2024</v>
       </c>
       <c r="I148" s="7" t="n">
-        <v>2868.017699504295</v>
+        <v>2122.132500443184</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>1108506048.964607</v>
+        <v>1323202667.338836</v>
       </c>
       <c r="K148" s="10" t="n">
         <v>142</v>
       </c>
       <c r="L148" s="10" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
@@ -8983,28 +8983,28 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>623525</v>
+        <v>1242822</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>MNE</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.556</v>
+        <v>0.111</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>13263.3281277699</v>
+        <v>3909.55892378182</v>
       </c>
       <c r="G149" s="8" t="n">
         <v>2026</v>
@@ -9013,16 +9013,16 @@
         <v>2024</v>
       </c>
       <c r="I149" s="7" t="n">
-        <v>1768.44375036932</v>
+        <v>977.389730945455</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>1102668889.44903</v>
+        <v>1214721460.193092</v>
       </c>
       <c r="K149" s="10" t="n">
         <v>143</v>
       </c>
       <c r="L149" s="10" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
@@ -9042,28 +9042,28 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
-        <v>1168722</v>
+        <v>928784</v>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0.111</v>
+        <v>0.444</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>3552.72335079222</v>
+        <v>6425.74151715712</v>
       </c>
       <c r="G150" s="8" t="n">
         <v>2026</v>
@@ -9072,16 +9072,16 @@
         <v>2024</v>
       </c>
       <c r="I150" s="7" t="n">
-        <v>888.180837698055</v>
+        <v>1285.148303431424</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>1038036484.996146</v>
+        <v>1193625181.854252</v>
       </c>
       <c r="K150" s="10" t="n">
         <v>144</v>
       </c>
       <c r="L150" s="10" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
@@ -9101,28 +9101,28 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>81938</v>
+        <v>5612817</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>49303.6491674336</v>
+        <v>851.497723870206</v>
       </c>
       <c r="G151" s="8" t="n">
         <v>2026</v>
@@ -9131,16 +9131,16 @@
         <v>2024</v>
       </c>
       <c r="I151" s="7" t="n">
-        <v>12325.9122918584</v>
+        <v>204.3594537288494</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>1009960601.370294</v>
+        <v>1147032216</v>
       </c>
       <c r="K151" s="10" t="n">
         <v>145</v>
       </c>
       <c r="L151" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
@@ -9160,28 +9160,28 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>928784</v>
+        <v>1168722</v>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>6425.74151715712</v>
+        <v>3552.72335079222</v>
       </c>
       <c r="G152" s="8" t="n">
         <v>2026</v>
@@ -9190,16 +9190,16 @@
         <v>2024</v>
       </c>
       <c r="I152" s="7" t="n">
-        <v>1070.956919526187</v>
+        <v>888.180837698055</v>
       </c>
       <c r="J152" s="5" t="n">
-        <v>994687651.5452096</v>
+        <v>1038036484.996146</v>
       </c>
       <c r="K152" s="10" t="n">
         <v>146</v>
       </c>
       <c r="L152" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
@@ -9219,28 +9219,28 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>5612817</v>
+        <v>81938</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>851.497723870206</v>
+        <v>49303.6491674336</v>
       </c>
       <c r="G153" s="8" t="n">
         <v>2026</v>
@@ -9249,16 +9249,16 @@
         <v>2024</v>
       </c>
       <c r="I153" s="7" t="n">
-        <v>170.2995447740412</v>
+        <v>12325.9122918584</v>
       </c>
       <c r="J153" s="5" t="n">
-        <v>955860179.9999996</v>
+        <v>1009960601.370294</v>
       </c>
       <c r="K153" s="10" t="n">
         <v>147</v>
       </c>
       <c r="L153" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
@@ -9278,28 +9278,28 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>417072</v>
+        <v>282467</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F154" s="7" t="n">
-        <v>7681.24400583113</v>
+        <v>26544.8707282621</v>
       </c>
       <c r="G154" s="8" t="n">
         <v>2026</v>
@@ -9308,16 +9308,16 @@
         <v>2024</v>
       </c>
       <c r="I154" s="7" t="n">
-        <v>1920.311001457783</v>
+        <v>3185.384487391452</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>800907950.0000004</v>
+        <v>899766000.0000013</v>
       </c>
       <c r="K154" s="10" t="n">
         <v>148</v>
       </c>
       <c r="L154" s="10" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
@@ -9337,28 +9337,28 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>14047786</v>
+        <v>634431</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>219.424830882698</v>
+        <v>6961.78955961526</v>
       </c>
       <c r="G155" s="8" t="n">
         <v>2026</v>
@@ -9367,16 +9367,16 @@
         <v>2024</v>
       </c>
       <c r="I155" s="7" t="n">
-        <v>54.8562077206745</v>
+        <v>1392.357911923052</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>770608266.8315831</v>
+        <v>883355022.4192539</v>
       </c>
       <c r="K155" s="10" t="n">
         <v>149</v>
       </c>
       <c r="L155" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
@@ -9396,28 +9396,28 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>282467</v>
+        <v>417072</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>26544.8707282621</v>
+        <v>7681.24400583113</v>
       </c>
       <c r="G156" s="8" t="n">
         <v>2026</v>
@@ -9426,16 +9426,16 @@
         <v>2024</v>
       </c>
       <c r="I156" s="7" t="n">
-        <v>2654.48707282621</v>
+        <v>1920.311001457783</v>
       </c>
       <c r="J156" s="5" t="n">
-        <v>749805000.0000012</v>
+        <v>800907950.0000004</v>
       </c>
       <c r="K156" s="10" t="n">
         <v>150</v>
       </c>
       <c r="L156" s="10" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
@@ -9455,28 +9455,28 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>634431</v>
+        <v>14047786</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>6961.78955961526</v>
+        <v>219.424830882698</v>
       </c>
       <c r="G157" s="8" t="n">
         <v>2026</v>
@@ -9485,16 +9485,16 @@
         <v>2024</v>
       </c>
       <c r="I157" s="7" t="n">
-        <v>1160.298259935877</v>
+        <v>54.8562077206745</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>736129185.3493781</v>
+        <v>770608266.8315831</v>
       </c>
       <c r="K157" s="10" t="n">
         <v>151</v>
       </c>
       <c r="L157" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
-        <v>5330690</v>
+        <v>791524</v>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>BTN</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F158" s="7" t="n">
-        <v>516.160999996036</v>
+        <v>3831.32535494609</v>
       </c>
       <c r="G158" s="8" t="n">
         <v>2026</v>
@@ -9544,16 +9544,16 @@
         <v>2024</v>
       </c>
       <c r="I158" s="7" t="n">
-        <v>129.040249999009</v>
+        <v>919.5180851870617</v>
       </c>
       <c r="J158" s="5" t="n">
-        <v>687873570.2672173</v>
+        <v>727820632.8596039</v>
       </c>
       <c r="K158" s="10" t="n">
         <v>152</v>
       </c>
       <c r="L158" s="10" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
@@ -9573,28 +9573,28 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>179744</v>
+        <v>5330690</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>St. Lucia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>14181.6303351598</v>
+        <v>516.160999996036</v>
       </c>
       <c r="G159" s="8" t="n">
         <v>2026</v>
@@ -9603,16 +9603,16 @@
         <v>2024</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>3545.40758378995</v>
+        <v>129.040249999009</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>637265740.7407408</v>
+        <v>687873570.2672173</v>
       </c>
       <c r="K159" s="10" t="n">
         <v>153</v>
       </c>
       <c r="L159" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
@@ -9632,28 +9632,28 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>791524</v>
+        <v>179744</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>BTN</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>St. Lucia</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>3831.32535494609</v>
+        <v>14181.6303351598</v>
       </c>
       <c r="G160" s="8" t="n">
         <v>2026</v>
@@ -9662,16 +9662,16 @@
         <v>2024</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>766.2650709892181</v>
+        <v>3545.40758378995</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>606517194.0496699</v>
+        <v>637265740.7407408</v>
       </c>
       <c r="K160" s="10" t="n">
         <v>154</v>
       </c>
       <c r="L160" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
@@ -9691,28 +9691,28 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>93772</v>
+        <v>2201352</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>23542.4526945578</v>
+        <v>1007.74151728028</v>
       </c>
       <c r="G161" s="8" t="n">
         <v>2026</v>
@@ -9721,16 +9721,16 @@
         <v>2024</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>5885.61317363945</v>
+        <v>251.93537932007</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>551905718.5185184</v>
+        <v>554598451.1369947</v>
       </c>
       <c r="K161" s="10" t="n">
         <v>155</v>
       </c>
       <c r="L161" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
@@ -9750,28 +9750,28 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>2201352</v>
+        <v>93772</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F162" s="7" t="n">
-        <v>1007.74151728028</v>
+        <v>23542.4526945578</v>
       </c>
       <c r="G162" s="8" t="n">
         <v>2026</v>
@@ -9780,16 +9780,16 @@
         <v>2024</v>
       </c>
       <c r="I162" s="7" t="n">
-        <v>235.1396873653987</v>
+        <v>5885.61317363945</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>517625221.0611951</v>
+        <v>551905718.5185184</v>
       </c>
       <c r="K162" s="10" t="n">
         <v>156</v>
       </c>
       <c r="L162" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
@@ -9809,28 +9809,28 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>33977</v>
+        <v>2337423</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>59879.7173015651</v>
+        <v>971.9077182482901</v>
       </c>
       <c r="G163" s="8" t="n">
         <v>2026</v>
@@ -9839,16 +9839,16 @@
         <v>2024</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>14969.92932539127</v>
+        <v>233.2578523795896</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>508633288.6888193</v>
+        <v>545222269.0826575</v>
       </c>
       <c r="K163" s="10" t="n">
         <v>157</v>
       </c>
       <c r="L163" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
@@ -9868,28 +9868,28 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
-        <v>2337423</v>
+        <v>33977</v>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F164" s="7" t="n">
-        <v>971.9077182482901</v>
+        <v>59879.7173015651</v>
       </c>
       <c r="G164" s="8" t="n">
         <v>2026</v>
@@ -9898,16 +9898,16 @@
         <v>2024</v>
       </c>
       <c r="I164" s="7" t="n">
-        <v>194.381543649658</v>
+        <v>14969.92932539127</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>454351890.9022146</v>
+        <v>508633288.6888193</v>
       </c>
       <c r="K164" s="10" t="n">
         <v>158</v>
       </c>
       <c r="L164" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
@@ -9957,10 +9957,10 @@
         <v>2024</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>145.2233819627156</v>
+        <v>174.2680583552588</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>400814791.5365117</v>
+        <v>480977749.843814</v>
       </c>
       <c r="K165" s="10" t="n">
         <v>159</v>
@@ -10016,10 +10016,10 @@
         <v>2024</v>
       </c>
       <c r="I166" s="7" t="n">
-        <v>692.330876434504</v>
+        <v>830.7970517214047</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>363388553.4303132</v>
+        <v>436066264.1163757</v>
       </c>
       <c r="K166" s="10" t="n">
         <v>160</v>
@@ -10045,28 +10045,28 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
-        <v>866628</v>
+        <v>819198</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F167" s="7" t="n">
-        <v>1662.75663312504</v>
+        <v>1933.55538435227</v>
       </c>
       <c r="G167" s="8" t="n">
         <v>2026</v>
@@ -10075,16 +10075,16 @@
         <v>2024</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>415.68915828126</v>
+        <v>464.0532922445448</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>360247863.8629718</v>
+        <v>380151528.9001466</v>
       </c>
       <c r="K167" s="10" t="n">
         <v>161</v>
       </c>
       <c r="L167" s="10" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
@@ -10104,28 +10104,28 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>117207</v>
+        <v>866628</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F168" s="7" t="n">
-        <v>11705.0902976658</v>
+        <v>1662.75663312504</v>
       </c>
       <c r="G168" s="8" t="n">
         <v>2026</v>
@@ -10134,16 +10134,16 @@
         <v>2024</v>
       </c>
       <c r="I168" s="7" t="n">
-        <v>2926.27257441645</v>
+        <v>415.68915828126</v>
       </c>
       <c r="J168" s="5" t="n">
-        <v>342979629.6296288</v>
+        <v>360247863.8629718</v>
       </c>
       <c r="K168" s="10" t="n">
         <v>162</v>
       </c>
       <c r="L168" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
@@ -10163,28 +10163,28 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>819198</v>
+        <v>117207</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>1933.55538435227</v>
+        <v>11705.0902976658</v>
       </c>
       <c r="G169" s="8" t="n">
         <v>2026</v>
@@ -10193,16 +10193,16 @@
         <v>2024</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>386.711076870454</v>
+        <v>2926.27257441645</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>316792940.7501222</v>
+        <v>342979629.6296288</v>
       </c>
       <c r="K169" s="10" t="n">
         <v>163</v>
       </c>
       <c r="L169" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
@@ -10222,28 +10222,28 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>218019</v>
+        <v>1400638</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>5392.87761915762</v>
+        <v>1331.9705130185</v>
       </c>
       <c r="G170" s="8" t="n">
         <v>2026</v>
@@ -10252,16 +10252,16 @@
         <v>2024</v>
       </c>
       <c r="I170" s="7" t="n">
-        <v>1348.219404789405</v>
+        <v>213.11528208296</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>293937446.4127813</v>
+        <v>298497362.4661129</v>
       </c>
       <c r="K170" s="10" t="n">
         <v>164</v>
       </c>
       <c r="L170" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
@@ -10281,28 +10281,28 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
-        <v>100616</v>
+        <v>218019</v>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>VCT</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>St. Vincent and the Grenadines</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>11501.2265187188</v>
+        <v>5392.87761915762</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>2026</v>
@@ -10311,10 +10311,10 @@
         <v>2024</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>2875.3066296797</v>
+        <v>1348.219404789405</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>289301851.8518527</v>
+        <v>293937446.4127813</v>
       </c>
       <c r="K171" s="10" t="n">
         <v>165</v>
@@ -10340,16 +10340,16 @@
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
-        <v>46843</v>
+        <v>100616</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>KNA</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>St. Kitts and Nevis</t>
+          <t>St. Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -10361,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>23960.6534357084</v>
+        <v>11501.2265187188</v>
       </c>
       <c r="G172" s="8" t="n">
         <v>2026</v>
@@ -10370,10 +10370,10 @@
         <v>2024</v>
       </c>
       <c r="I172" s="7" t="n">
-        <v>5990.1633589271</v>
+        <v>2875.3066296797</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>280597222.2222221</v>
+        <v>289301851.8518527</v>
       </c>
       <c r="K172" s="10" t="n">
         <v>166</v>
@@ -10399,28 +10399,28 @@
     </row>
     <row r="173">
       <c r="A173" s="5" t="n">
-        <v>1400638</v>
+        <v>46843</v>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>KNA</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>St. Kitts and Nevis</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>1331.9705130185</v>
+        <v>23960.6534357084</v>
       </c>
       <c r="G173" s="8" t="n">
         <v>2026</v>
@@ -10429,16 +10429,16 @@
         <v>2024</v>
       </c>
       <c r="I173" s="7" t="n">
-        <v>177.5960684024667</v>
+        <v>5990.1633589271</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>248747802.0550941</v>
+        <v>280597222.2222221</v>
       </c>
       <c r="K173" s="10" t="n">
         <v>167</v>
       </c>
       <c r="L173" s="10" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
@@ -10488,10 +10488,10 @@
         <v>2024</v>
       </c>
       <c r="I174" s="7" t="n">
-        <v>568.4617052784949</v>
+        <v>682.154046334194</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>186328672.3710693</v>
+        <v>223594406.8452831</v>
       </c>
       <c r="K174" s="10" t="n">
         <v>168</v>
@@ -10576,28 +10576,28 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
-        <v>104175</v>
+        <v>235536</v>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>5651.59373063157</v>
+        <v>3490.56883486557</v>
       </c>
       <c r="G176" s="8" t="n">
         <v>2026</v>
@@ -10606,16 +10606,16 @@
         <v>2024</v>
       </c>
       <c r="I176" s="7" t="n">
-        <v>1412.898432657892</v>
+        <v>698.113766973114</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>147188694.222136</v>
+        <v>164430924.2177794</v>
       </c>
       <c r="K176" s="10" t="n">
         <v>170</v>
       </c>
       <c r="L176" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
@@ -10635,28 +10635,28 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
-        <v>235536</v>
+        <v>104175</v>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>3490.56883486557</v>
+        <v>5651.59373063157</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>2026</v>
@@ -10665,16 +10665,16 @@
         <v>2024</v>
       </c>
       <c r="I177" s="7" t="n">
-        <v>581.7614724775949</v>
+        <v>1412.898432657892</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>137025770.1814828</v>
+        <v>147188694.222136</v>
       </c>
       <c r="K177" s="10" t="n">
         <v>171</v>
       </c>
       <c r="L177" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
@@ -10753,28 +10753,28 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
-        <v>134518</v>
+        <v>121354</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>KIR</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0.111</v>
+        <v>0.889</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>2288.63471423684</v>
+        <v>17858.8226383978</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>2026</v>
@@ -10783,16 +10783,16 @@
         <v>2024</v>
       </c>
       <c r="I179" s="7" t="n">
-        <v>572.15867855921</v>
+        <v>714.3529055359122</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>76965641.12242781</v>
+        <v>86689582.49840508</v>
       </c>
       <c r="K179" s="10" t="n">
         <v>173</v>
       </c>
       <c r="L179" s="10" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
@@ -10812,16 +10812,16 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
-        <v>37548</v>
+        <v>134518</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>MHL</t>
+          <t>KIR</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>7726.33668877794</v>
+        <v>2288.63471423684</v>
       </c>
       <c r="G180" s="8" t="n">
         <v>2026</v>
@@ -10842,16 +10842,16 @@
         <v>2024</v>
       </c>
       <c r="I180" s="7" t="n">
-        <v>1931.584172194485</v>
+        <v>572.15867855921</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>72527122.49755852</v>
+        <v>76965641.12242781</v>
       </c>
       <c r="K180" s="10" t="n">
         <v>174</v>
       </c>
       <c r="L180" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
@@ -10871,28 +10871,28 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
-        <v>121354</v>
+        <v>37548</v>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>MHL</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>17858.8226383978</v>
+        <v>7726.33668877794</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>2026</v>
@@ -10901,16 +10901,16 @@
         <v>2024</v>
       </c>
       <c r="I181" s="7" t="n">
-        <v>595.2940879465935</v>
+        <v>1931.584172194485</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>72241318.74867092</v>
+        <v>72527122.49755852</v>
       </c>
       <c r="K181" s="10" t="n">
         <v>175</v>
       </c>
       <c r="L181" s="10" t="n">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
@@ -11107,16 +11107,16 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
-        <v>1866124</v>
+        <v>5395790</v>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -11128,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="F185" s="7" t="n">
-        <v>23409.0845154775</v>
+        <v>112894.953240805</v>
       </c>
       <c r="G185" s="8" t="n">
         <v>2026</v>
@@ -11166,16 +11166,16 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>5572279</v>
+        <v>1866124</v>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -11187,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="F186" s="7" t="n">
-        <v>86785.4334489176</v>
+        <v>23409.0845154775</v>
       </c>
       <c r="G186" s="8" t="n">
         <v>2026</v>
@@ -11225,28 +11225,28 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="n">
-        <v>5619911</v>
+        <v>11858610</v>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F187" s="7" t="n">
-        <v>53149.7671934051</v>
+        <v>56614.5679499036</v>
       </c>
       <c r="G187" s="8" t="n">
         <v>2026</v>
@@ -11284,16 +11284,16 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
-        <v>10569709</v>
+        <v>5976992</v>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -11305,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="F188" s="7" t="n">
-        <v>57117.4877440616</v>
+        <v>71026.4832271897</v>
       </c>
       <c r="G188" s="8" t="n">
         <v>2026</v>
@@ -11343,28 +11343,28 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
-        <v>11858610</v>
+        <v>1372341</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F189" s="7" t="n">
-        <v>56614.5679499036</v>
+        <v>31428.3547816104</v>
       </c>
       <c r="G189" s="8" t="n">
         <v>2026</v>
@@ -11402,16 +11402,16 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>5395790</v>
+        <v>5619911</v>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -11423,7 +11423,7 @@
         <v>1</v>
       </c>
       <c r="F190" s="7" t="n">
-        <v>112894.953240805</v>
+        <v>53149.7671934051</v>
       </c>
       <c r="G190" s="8" t="n">
         <v>2026</v>
@@ -11461,28 +11461,28 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="n">
-        <v>677012</v>
+        <v>5572279</v>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>137781.681659123</v>
+        <v>86785.4334489176</v>
       </c>
       <c r="G191" s="8" t="n">
         <v>2026</v>
@@ -11520,28 +11520,28 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="n">
-        <v>5976992</v>
+        <v>677012</v>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F192" s="7" t="n">
-        <v>71026.4832271897</v>
+        <v>137781.681659123</v>
       </c>
       <c r="G192" s="8" t="n">
         <v>2026</v>
@@ -11579,16 +11579,16 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="n">
-        <v>1372341</v>
+        <v>10569709</v>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
@@ -11600,7 +11600,7 @@
         <v>1</v>
       </c>
       <c r="F193" s="7" t="n">
-        <v>31428.3547816104</v>
+        <v>57117.4877440616</v>
       </c>
       <c r="G193" s="8" t="n">
         <v>2026</v>
@@ -11952,9 +11952,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A202:O202"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
